--- a/public/roadpro/RoadPro_Shortcuts.xlsx
+++ b/public/roadpro/RoadPro_Shortcuts.xlsx
@@ -183,9 +183,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -551,25 +549,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RoadPro v2.6 - Shortcut Keys</t>
+          <t>RoadPro v3.0 - Shortcut Keys</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AutoCAD road builder plugin  |  05-Oct-2026  |  Developed by https://www.exceltokml.com/</t>
+          <t>AutoCAD road builder plugin  |  07-Oct-2026  |  Developed by https://www.exceltokml.com/</t>
         </is>
       </c>
     </row>
@@ -682,7 +680,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>RDW</t>
@@ -695,11 +693,11 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Lane widening: extra lane from start to end chainage that comes back, straight or curve taper, fillet or direct link</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
+          <t>Lane widening: extra lane from start to end chainage that comes back, straight or curve taper, fillet or direct link. Both sides can use different chainages and radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>RDT</t>
@@ -712,69 +710,77 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Road taper: wider (+) or narrower (-) from any start to any end chainage, new width continues to the road end</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+          <t>Road taper: wider (+) or narrower (-) from any start to any end chainage, new width continues to the road end. Both sides can use different chainages and radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>RDJ</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>ROADJUNCTION</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Road junction / tie-in: join a new road with kerb-return radius, opened edge, corner surface, barricades, STOP / GIVE WAY and turning-area markings</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>RDM</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>ROADMARK</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Road markings: white edge lines and lane line (broken 3 m / 6 m, solid on bends and junction approaches). Draw again to refresh, or Remove</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ROADPRORESET</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Restore all settings to defaults (no shortcut, on purpose, so you don't reset by accident)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Useful AutoCAD keys while using RoadPro</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Use</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Undo the whole road in one step</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Open the command history to see the summary and the Excel file path</t>
         </is>
       </c>
       <c r="C18" s="11" t="n"/>
@@ -782,12 +788,12 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Finish drawing the centre line, or skip a prompt (such as placing tables)</t>
+          <t>Undo the whole road in one step</t>
         </is>
       </c>
       <c r="C19" s="11" t="n"/>
@@ -795,12 +801,12 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Esc</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Cancel the command</t>
+          <t>Open the command history to see the summary and the Excel file path</t>
         </is>
       </c>
       <c r="C20" s="11" t="n"/>
@@ -808,25 +814,51 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>Enter</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Finish drawing the centre line, or skip a prompt (such as placing tables)</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Esc</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Cancel the command</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>APPLOAD</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Load RoadPro.lsp, or add it to the Startup Suite</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Note: RDR, RDRAD, RDSEC, RDX, RDW and RDT all start by asking you to select the road's centre line (layer ROAD-CL). Turning radius is measured at the centre line by default.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="C23" s="11" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Note: RDR, RDRAD, RDSEC, RDX, RDW, RDT, RDJ and RDM all start by asking you to select the road's centre line (layer ROAD-CL). Turning radius is measured at the centre line by default. Chainage boxes accept 100 or 0+100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Developed by https://www.exceltokml.com/</t>
         </is>
@@ -836,25 +868,25 @@
   <mergeCells count="12">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;9 RoadPro v2.6  |  Developed by https://www.exceltokml.com/</oddFooter>
+    <oddFooter>&amp;C&amp;9 RoadPro v3.0  |  Developed by https://www.exceltokml.com/</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/public/roadpro/RoadPro_Shortcuts.xlsx
+++ b/public/roadpro/RoadPro_Shortcuts.xlsx
@@ -560,14 +560,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RoadPro v3.0 - Shortcut Keys</t>
+          <t>RoadPro v3.2 - Shortcut Keys</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AutoCAD road builder plugin  |  07-Oct-2026  |  Developed by https://www.exceltokml.com/</t>
+          <t>AutoCAD road builder plugin  |  09-Oct-2026  |  Developed by https://www.exceltokml.com/</t>
         </is>
       </c>
     </row>
@@ -850,10 +850,10 @@
       </c>
       <c r="C23" s="11" t="n"/>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="44" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Note: RDR, RDRAD, RDSEC, RDX, RDW, RDT, RDJ and RDM all start by asking you to select the road's centre line (layer ROAD-CL). Turning radius is measured at the centre line by default. Chainage boxes accept 100 or 0+100.</t>
+          <t>Note: RDR, RDRAD, RDSEC, RDX, RDW, RDT, RDJ and RDM all start by asking you to select the road's centre line (layer ROAD-CL). Turning radius: Match existing (default) or Manual, measured at the centre line. Chainage boxes accept 100 or 0+100. Sign sizes, warning distances and line patterns follow Oman HDS 2017 Sec.19 (check QTCM in Qatar).</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;9 RoadPro v3.0  |  Developed by https://www.exceltokml.com/</oddFooter>
+    <oddFooter>&amp;C&amp;9 RoadPro v3.2  |  Developed by https://www.exceltokml.com/</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/public/roadpro/RoadPro_Shortcuts.xlsx
+++ b/public/roadpro/RoadPro_Shortcuts.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -560,14 +560,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RoadPro v3.2 - Shortcut Keys</t>
+          <t>RoadPro v3.3 - Shortcut Keys</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AutoCAD road builder plugin  |  09-Oct-2026  |  Developed by https://www.exceltokml.com/</t>
+          <t>AutoCAD road builder plugin  |  12-Oct-2026  |  Developed by https://www.exceltokml.com/</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="46" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>RDW</t>
@@ -693,11 +693,11 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Lane widening: extra lane from start to end chainage that comes back, straight or curve taper, fillet or direct link. Both sides can use different chainages and radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
+          <t>Lane widening: extra lane from start to end chainage that comes back, straight or curve taper, fillet or direct link. Both sides can use different chainages and radius. Barricades, cones and kerb move to the new edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>RDT</t>
@@ -710,11 +710,11 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Road taper: wider (+) or narrower (-) from any start to any end chainage, new width continues to the road end. Both sides can use different chainages and radius</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
+          <t>Road taper: wider (+) or narrower (-) from any start to any end chainage, new width continues to the road end. Both sides can use different chainages and radius. Barricades, cones and kerb follow the new edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>RDJ</t>
@@ -727,7 +727,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Road junction / tie-in: join a new road with kerb-return radius, opened edge, corner surface, barricades, STOP / GIVE WAY and turning-area markings</t>
+          <t>Road junction / tie-in: join a new road with kerb-return radius, opened edge, corner surface, corner treatment (same as main road, barricades, traffic cones or kerb stone), STOP / GIVE WAY, turning-area markings, auxiliary lane and island</t>
         </is>
       </c>
     </row>
@@ -744,121 +744,145 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Road markings: white edge lines and lane line (broken 3 m / 6 m, solid on bends and junction approaches). Draw again to refresh, or Remove</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+          <t>Road markings: white centre line (L1 / L2 / L2A by speed, or double / single continuous), yellow L4 edge lines, arrows. Draw again to refresh, or Remove</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>RDL</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>ROADLINE</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>NEW in 3.3 - Single line: one run of barricades, traffic cones or kerb stone along any line, polyline, arc, spline, circle or ellipse. On the line, offset left / right or both sides, from / to distance, quantity label</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>ROADPRORESET</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Restore all settings to defaults (no shortcut, on purpose, so you don't reset by accident)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Useful AutoCAD keys while using RoadPro</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Use</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="C19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Undo the whole road in one step</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="C20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Open the command history to see the summary and the Excel file path</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="C21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Enter</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Finish drawing the centre line, or skip a prompt (such as placing tables)</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="C22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Esc</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Cancel the command</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="C23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>APPLOAD</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Load RoadPro.lsp, or add it to the Startup Suite</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n"/>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Note: RDR, RDRAD, RDSEC, RDX, RDW, RDT, RDJ and RDM all start by asking you to select the road's centre line (layer ROAD-CL). Turning radius: Match existing (default) or Manual, measured at the centre line. Chainage boxes accept 100 or 0+100. Sign sizes, warning distances and line patterns follow Oman HDS 2017 Sec.19 (check QTCM in Qatar).</t>
+      <c r="C24" s="11" t="n"/>
+    </row>
+    <row r="26" ht="78" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Note: RDR, RDRAD, RDSEC, RDX, RDW, RDT, RDJ and RDM start by asking you to select the road's centre line (layer ROAD-CL). RDL works on any line you select. Edge treatment: barricades, traffic cones or kerb stone. Chainage boxes accept 100 or 0+100. Sign sizes, warning distances and line patterns follow Oman HDS 2017 Sec.19 (check QTCM in Qatar). Full step-by-step manual: RoadPro_User_Guide.pdf</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.exceltokml.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Developed by https://www.exceltokml.com/</t>
         </is>
@@ -866,17 +890,17 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A17:C17"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="B18:C18"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <hyperlinks>
@@ -886,7 +910,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;9 RoadPro v3.2  |  Developed by https://www.exceltokml.com/</oddFooter>
+    <oddFooter>&amp;C&amp;9 RoadPro v3.3  |  Developed by https://www.exceltokml.com/</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/public/roadpro/RoadPro_Shortcuts.xlsx
+++ b/public/roadpro/RoadPro_Shortcuts.xlsx
@@ -116,6 +116,19 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="00C9CDD1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9CDD1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9CDD1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="00C9CDD1"/>
@@ -132,19 +145,6 @@
         <color rgb="00C9CDD1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C9CDD1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9CDD1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9CDD1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -179,7 +179,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -560,14 +560,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RoadPro v3.3 - Shortcut Keys</t>
+          <t>RoadPro v3.4 - Shortcut Keys</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AutoCAD road builder plugin  |  12-Oct-2026  |  Developed by https://www.exceltokml.com/</t>
+          <t>AutoCAD road builder plugin  |  23-Oct-2026  |  Developed by https://www.exceltokml.com/</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="46" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>RDW</t>
@@ -714,7 +714,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="46" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>RDJ</t>
@@ -731,7 +731,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
+    <row r="14" ht="46" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>RDM</t>
@@ -749,140 +749,242 @@
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>RDL</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ROADLINE</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>NEW in 3.3 - Single line: one run of barricades, traffic cones or kerb stone along any line, polyline, arc, spline, circle or ellipse. On the line, offset left / right or both sides, from / to distance, quantity label</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Single line: one run of barricades, traffic cones or kerb stone along any line, polyline, arc, spline, circle or ellipse. On the line, offset left / right or both sides, from / to distance, quantity label</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>RDC</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>ROADCORRIDOR</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>NEW in 3.4 - Corridor of an existing road: lanes (automatic from traffic volume or manual, left and right can differ), single or dual carriageway, flush or raised median, sidewalks and walkways left / right with interlocking paver hatch, drains, utility corridors</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>RDU</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>ROADUPDATE</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>NEW in 3.4 - Redraw the corridor (median, sidewalks, walkways, drains, utilities) after the road was edited, with the settings stored on the road</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>RDER</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>ROADEDITRADIUS</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>NEW in 3.4 - Change a curve radius after the road is built (one curve or All). Checks the radius fits between the straights, then rebuilds the road. One U undoes it</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>RDB</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>ROADREBUILD</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>NEW in 3.4 - Rebuild the whole road from its centre line after you edited the CL with grips, Properties or PEDIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>RDLX</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>ROADLANDXML</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>NEW in 3.4 - Export the centre line as a LandXML 1.2 alignment (lines + arcs, start station) for Civil 3D: Insert &gt; LandXML</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>RDLXI</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>ROADLANDXMLIN</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>NEW in 3.4 - Import a LandXML alignment (for example exported from Civil 3D) as a polyline you can use as a RoadPro centre line</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>ROADPRORESET</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Restore all settings to defaults (no shortcut, on purpose, so you don't reset by accident)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Useful AutoCAD keys while using RoadPro</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Use</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="C25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Undo the whole road in one step</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="C26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Open the command history to see the summary and the Excel file path</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="C27" s="11" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Enter</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Finish drawing the centre line, or skip a prompt (such as placing tables)</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="C28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Esc</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Cancel the command</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="C29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>APPLOAD</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Load RoadPro.lsp, or add it to the Startup Suite</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n"/>
-    </row>
-    <row r="26" ht="78" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Note: RDR, RDRAD, RDSEC, RDX, RDW, RDT, RDJ and RDM start by asking you to select the road's centre line (layer ROAD-CL). RDL works on any line you select. Edge treatment: barricades, traffic cones or kerb stone. Chainage boxes accept 100 or 0+100. Sign sizes, warning distances and line patterns follow Oman HDS 2017 Sec.19 (check QTCM in Qatar). Full step-by-step manual: RoadPro_User_Guide.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="C30" s="11" t="n"/>
+    </row>
+    <row r="32" ht="110" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Note: RDR, RDRAD, RDSEC, RDX, RDW, RDT, RDJ, RDM, RDC, RDU, RDER, RDB and RDLX start by asking you to select the road's centre line (layer ROAD-CL). RDL works on any line you select. RDP can follow an existing polyline (original kept, checked for short segments, sharp bends and self-intersections) or a picked line, and accepts a Civil 3D alignment (copied as a polyline - not a live link). Edge treatment: barricades, traffic cones or kerb stone. Chainage boxes accept 100 or 0+100. Automatic lane counts are indicative only, not an engineering approval. Drains and utility corridors are geometric provisions only (no hydraulic design). Sign sizes, warning distances and line patterns follow Oman HDS 2017 Sec.19 (check QTCM in Qatar). Full step-by-step manual: RoadPro_User_Guide.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>https://www.exceltokml.com/</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Developed by https://www.exceltokml.com/</t>
         </is>
@@ -890,31 +992,23 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;9 RoadPro v3.3  |  Developed by https://www.exceltokml.com/</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>